--- a/solvent/solvent.xlsx
+++ b/solvent/solvent.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c922c6a9738126/Documents/Desktop/SepCal_Portfolio/solvent/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_F25DC773A252ABDACC10480E095A4B565BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B77E9C01-58D4-4B89-93FC-6105243B89C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACEF7EF-9765-4C25-96A5-E0459366ACD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="acetone" sheetId="1" r:id="rId1"/>
-    <sheet name="ethanol" sheetId="2" r:id="rId2"/>
+    <sheet name="B" sheetId="1" r:id="rId1"/>
+    <sheet name="C" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -616,13 +616,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -638,7 +638,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>10</v>
       </c>
@@ -647,7 +647,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>20</v>
       </c>
@@ -655,7 +655,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>30</v>
       </c>
@@ -664,7 +664,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>40</v>
       </c>
@@ -672,7 +672,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>50</v>
       </c>
@@ -681,7 +681,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>60</v>
       </c>
@@ -689,7 +689,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>70</v>
       </c>
@@ -698,7 +698,7 @@
         <v>731.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>80</v>
       </c>
@@ -706,7 +706,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>90</v>
       </c>
@@ -715,7 +715,7 @@
         <v>704.3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>100</v>
       </c>
@@ -734,13 +734,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8F260-2A58-4D46-8946-55BA03AE28BB}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -756,7 +756,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>10</v>
       </c>
@@ -765,7 +765,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>30</v>
       </c>
@@ -783,7 +783,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>40</v>
       </c>
@@ -792,7 +792,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>50</v>
       </c>
@@ -801,7 +801,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>60</v>
       </c>
@@ -810,7 +810,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>70</v>
       </c>
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>80</v>
       </c>
@@ -828,7 +828,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>90</v>
       </c>
@@ -837,7 +837,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>100</v>
       </c>
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D13" s="4"/>
     </row>
   </sheetData>
